--- a/LTN_2026_Donations.xlsx
+++ b/LTN_2026_Donations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackH\Documents\Blood Cancer United\LTN_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA03C27D-FC12-4B35-8E5E-A60EE85A4B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C847FD-634F-45C2-A5BC-5ACF740D2C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11175" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
   </bookViews>
@@ -39,15 +39,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>Donor</t>
   </si>
   <si>
     <t>Donation Amount</t>
-  </si>
-  <si>
-    <t>person 1</t>
   </si>
 </sst>
 </file>
@@ -441,11 +438,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E825204A-042E-49AE-8958-CC460986F1C1}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -456,14 +453,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1">
-        <v>8000</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LTN_2026_Donations.xlsx
+++ b/LTN_2026_Donations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackH\Documents\Blood Cancer United\LTN_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C847FD-634F-45C2-A5BC-5ACF740D2C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C13A3A-0E2E-4BE6-AACA-BB47AF5EEEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11175" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Donor</t>
   </si>
   <si>
     <t>Donation Amount</t>
+  </si>
+  <si>
+    <t>Juli Stevens</t>
+  </si>
+  <si>
+    <t>Kirsty Peev</t>
+  </si>
+  <si>
+    <t>Anonymous</t>
+  </si>
+  <si>
+    <t>Mike Zane</t>
+  </si>
+  <si>
+    <t>Andrew Bakker</t>
   </si>
 </sst>
 </file>
@@ -438,10 +453,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E825204A-042E-49AE-8958-CC460986F1C1}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -453,6 +468,46 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LTN_2026_Donations.xlsx
+++ b/LTN_2026_Donations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackH\Documents\Blood Cancer United\LTN_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C13A3A-0E2E-4BE6-AACA-BB47AF5EEEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB6AC1B-4ED9-40D4-8B82-139D56613BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Donor</t>
   </si>
@@ -60,6 +60,15 @@
   </si>
   <si>
     <t>Andrew Bakker</t>
+  </si>
+  <si>
+    <t>Rachel Doan</t>
+  </si>
+  <si>
+    <t>Gabrielle Halpern</t>
+  </si>
+  <si>
+    <t>Sam Feldman</t>
   </si>
 </sst>
 </file>
@@ -453,10 +462,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E825204A-042E-49AE-8958-CC460986F1C1}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -508,6 +517,30 @@
         <v>50</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>216</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LTN_2026_Donations.xlsx
+++ b/LTN_2026_Donations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackH\Documents\Blood Cancer United\LTN_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB6AC1B-4ED9-40D4-8B82-139D56613BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F583A2D4-80F1-4E2B-B2AC-F7C34DD358DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Donor</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>Sam Feldman</t>
+  </si>
+  <si>
+    <t>Naomi Feldman</t>
   </si>
 </sst>
 </file>
@@ -462,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E825204A-042E-49AE-8958-CC460986F1C1}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -541,6 +544,14 @@
         <v>216</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>180</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LTN_2026_Donations.xlsx
+++ b/LTN_2026_Donations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackH\Documents\Blood Cancer United\LTN_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F583A2D4-80F1-4E2B-B2AC-F7C34DD358DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CC4BA7-3550-4C58-BAE5-2F4F0510B2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Donor</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>Naomi Feldman</t>
+  </si>
+  <si>
+    <t>Clarissa Halpern</t>
+  </si>
+  <si>
+    <t>Talia Feldman</t>
   </si>
 </sst>
 </file>
@@ -465,14 +471,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E825204A-042E-49AE-8958-CC460986F1C1}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.81640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -480,7 +486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -488,7 +494,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -496,7 +502,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -504,7 +510,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -512,7 +518,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -520,7 +526,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -528,7 +534,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -536,7 +542,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -544,12 +550,28 @@
         <v>216</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="1">
         <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
